--- a/com.mybank.ParaBank/src/test/resources/TestData.xlsx
+++ b/com.mybank.ParaBank/src/test/resources/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\eclipse-workspace\com.mybank.ParaBank\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\git\repository\ParaBankProject\com.mybank.ParaBank\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FB68F2-0E6F-43C6-8DAB-FA1698C58FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B289851D-A301-44F4-BEBF-84D5DA1E56CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -791,7 +791,7 @@
         <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
         <v>58</v>
